--- a/InputFiles/CDS/TC01_CDS_phs00422532_StudyName-IvyGlioblastomaAtlasProject_StudyDataTypes-Imaging.xlsx
+++ b/InputFiles/CDS/TC01_CDS_phs00422532_StudyName-IvyGlioblastomaAtlasProject_StudyDataTypes-Imaging.xlsx
@@ -516,46 +516,46 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>SELECT
-    sp.participant_id AS "Participant ID", 
-    s.study_name AS "Study Name",
-    s.phs_accession AS "Accession",
-    sp.sex AS "Sex",
-    '' AS "Samples"
-FROM 
-    df_participant sp
-JOIN 
-    df_study s ON sp."study.study_id" = s.study_id
-JOIN 
-    df_file f1 ON f1."participant.study_participant_id" = sp.study_participant_id
-WHERE 
-    s.phs_accession = 'phs004225' AND s.study_name = 'Ivy Glioblastoma Atlas Project' AND s.study_data_types = 'Imaging'
-GROUP BY
-    sp.participant_id, 
-    s.study_name,
-    s.phs_accession,
-    sp.sex
-ORDER BY 
-    sp.participant_id ASC
-LIMIT 100;</t>
+          <t xml:space="preserve">MATCH (p:participant)-[:of_study]-&gt;(s:study)
+WHERE s.phs_accession = "phs004225"
+  AND s.study_name = "Ivy Glioblastoma Atlas Project"
+  AND s.study_data_types CONTAINS "Imaging"
+WITH DISTINCT p, s
+OPTIONAL MATCH (samp_all:sample)-[:of_participant]-&gt;(p)
+WITH p, s, samp_all
+ORDER BY samp_all.sample_id ASC
+WITH p, s, [x IN collect(samp_all.sample_id) WHERE x IS NOT NULL] AS sample_ids
+WITH p, s, sample_ids,
+  CASE
+    WHEN size(sample_ids) &gt; 5
+    THEN reduce(acc = "", id IN sample_ids[0..5] | CASE WHEN acc = "" THEN id ELSE acc + ", " + id END) + ", ..."
+    ELSE reduce(acc = "", id IN sample_ids | CASE WHEN acc = "" THEN id ELSE acc + ", " + id END)
+  END AS samples
+RETURN
+  p.participant_id AS participant_id,
+  s.study_name AS study_name,
+  s.phs_accession AS accession,
+  p.sex AS sex,
+  samples
+ORDER BY p.participant_id ASC
+LIMIT 100
+</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>SELECT
-    COUNT(DISTINCT s.study_name) AS "Studies",
-    COUNT(DISTINCT sp.participant_id) AS "Participants",
-    0 AS "Samples",
-    FORMAT(COUNT(DISTINCT f1.file_id), 'N0') AS "Files"
-FROM 
-    df_participant sp
-JOIN 
-    df_study s ON sp."study.study_id" = s.study_id
-JOIN 
-    df_file f1 ON f1."participant.study_participant_id" = sp.study_participant_id
-WHERE 
-    s.phs_accession = 'phs004225'
-    AND s.study_name = 'Ivy Glioblastoma Atlas Project' AND s.study_data_types = 'Imaging';</t>
+          <t xml:space="preserve">MATCH (p:participant)-[:of_study]-&gt;(s:study)
+WHERE s.phs_accession = "phs004225"
+  AND s.study_name = "Ivy Glioblastoma Atlas Project"
+  AND s.study_data_types CONTAINS "Imaging"
+OPTIONAL MATCH (samp:sample)-[:of_participant]-&gt;(p)
+OPTIONAL MATCH (f:file)-[:of_participant]-&gt;(p)
+RETURN
+  count(DISTINCT s) AS Studies,
+  count(DISTINCT p) AS Participants,
+  count(DISTINCT samp) AS Samples,
+  count(DISTINCT f) AS Files
+</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -577,29 +577,21 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SELECT
-	s.study_name AS "Study Name",
-	s.phs_accession AS "Accession",
-	f1.file_name AS "File Name",
-	f1.file_id AS "File ID",
-	f1.file_type AS "File Type",
-            'Not Applicable' AS "Sample ID"
-FROM 
-    df_participant sp
-INNER JOIN 
-    df_study s ON sp."study.study_id" = s.study_id
-INNER JOIN  
-    df_file f1 ON f1."participant.study_participant_id" = sp.study_participant_id
-WHERE 
-    s.phs_accession = 'phs004225' AND s.study_name = 'Ivy Glioblastoma Atlas Project' AND s.study_data_types = 'Imaging'
-GROUP BY
-    s.study_name,
-    s.phs_accession,
-    f1.file_name,
-    f1.file_type
-ORDER BY 
-    f1.file_name ASC
-LIMIT 100;</t>
+          <t xml:space="preserve">MATCH (f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+WHERE s.phs_accession = "phs004225"
+  AND s.study_name = "Ivy Glioblastoma Atlas Project"
+  AND s.study_data_types CONTAINS "Imaging"
+OPTIONAL MATCH (f)-[:from_sample]-&gt;(samp:sample)
+RETURN
+  s.study_name AS study_name,
+  s.phs_accession AS accession,
+  f.file_name AS file_name,
+  f.file_id AS file_id,
+  f.file_type AS file_type,
+  COALESCE(samp.sample_id, "Not Applicable") AS sample_id
+ORDER BY f.file_name ASC
+LIMIT 100
+</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
